--- a/results/问题三_参考口径/结果提交_主方案.xlsx
+++ b/results/问题三_参考口径/结果提交_主方案.xlsx
@@ -1288,23 +1288,23 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>S001-MED-01,S001-MED-02,S001-WAT-03,S001-WAT-05,S001-WAT-08,S001-FOD-01,S001-FOD-02,S001-HYG-01,S001-HYG-02</t>
+          <t>S001-WAT-04,S001-WAT-06,S001-WAT-07,S001-WAT-08,S001-FOD-02,S001-HYG-01,S001-HYG-02</t>
         </is>
       </c>
       <c r="E2" s="7" t="n">
         <v>76</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.231</v>
+        <v>0.206</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>1122.169077324681</v>
+        <v>1559.280847221722</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>2.917582307550811</v>
+        <v>2.917026126174722</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>63.53022115561486</v>
+        <v>63.53717342281598</v>
       </c>
     </row>
     <row r="3">
@@ -1325,23 +1325,23 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>S001-WAT-01,S001-WAT-02,S001-WAT-04,S001-WAT-06,S001-WAT-07,S001-FOD-03</t>
+          <t>S001-MED-01,S001-MED-02,S001-WAT-01,S001-WAT-02,S001-WAT-03,S001-WAT-05,S001-FOD-01,S001-FOD-03</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
         <v>78</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>0.163</v>
+        <v>0.188</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>1014.169077324681</v>
+        <v>1625.280847221722</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>2.995769262690981</v>
+        <v>2.995205315576006</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>62.55288421636273</v>
+        <v>62.55993355529993</v>
       </c>
     </row>
     <row r="4">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>S002-WAT-01,S002-WAT-03,S002-WAT-04,S002-FOD-02,S002-HYG-01</t>
+          <t>S002-WAT-01,S002-WAT-02,S002-WAT-04,S002-FOD-02,S002-HYG-01</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
@@ -1372,13 +1372,13 @@
         <v>0.144</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1591.812384805955</v>
+        <v>2041.524362647923</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>5.721224670804878</v>
+        <v>5.720921442330927</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>28.48469161493903</v>
+        <v>28.48848197086341</v>
       </c>
     </row>
     <row r="5">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>S002-MED-01,S002-WAT-02,S002-FOD-01</t>
+          <t>S002-MED-01,S002-WAT-03,S002-FOD-01</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -1409,13 +1409,13 @@
         <v>0.067</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1426.694300089159</v>
+        <v>1816.459573829564</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.713422287413139</v>
+        <v>2.713245988918413</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>32.16444281467152</v>
+        <v>32.16885027703967</v>
       </c>
     </row>
     <row r="6">
@@ -1431,28 +1431,28 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>S003-MED-01,S003-WAT-04,S003-FOD-02</t>
+          <t>S003-WAT-01,S003-WAT-02,S003-WAT-04,S003-FOD-01,S003-HYG-01</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.067</v>
+        <v>0.144</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1690.523303498377</v>
+        <v>2369.158540771288</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>2.779917467852169</v>
+        <v>5.764472432678109</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>30.50206330369578</v>
+        <v>27.94409459152364</v>
       </c>
     </row>
     <row r="7">
@@ -1468,28 +1468,28 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-FOD-01,S003-HYG-01</t>
+          <t>S003-MED-01,S003-WAT-03,S003-FOD-02</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.144</v>
+        <v>0.067</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1920.091349559575</v>
+        <v>2079.763198262336</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5.764965114940174</v>
+        <v>2.779564957804763</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>27.93793606324783</v>
+        <v>30.51087605488092</v>
       </c>
     </row>
     <row r="8">
@@ -1520,13 +1520,13 @@
         <v>0.156</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1821.056692482148</v>
+        <v>2302.999275080975</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>6.152932018901095</v>
+        <v>6.153272635381178</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>23.08834976373631</v>
+        <v>23.08409205773527</v>
       </c>
     </row>
     <row r="9">
@@ -1557,13 +1557,13 @@
         <v>0.156</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1397.190524525376</v>
+        <v>1872.631861406162</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4.222192859504678</v>
+        <v>4.220623405290876</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>47.22258925619153</v>
+        <v>47.24220743386405</v>
       </c>
     </row>
     <row r="10">
@@ -1594,13 +1594,13 @@
         <v>0.156</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1081.55386793656</v>
+        <v>1569.336359160239</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>2.597987864766336</v>
+        <v>2.600046403924214</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>67.5251516904208</v>
+        <v>67.49941995094733</v>
       </c>
     </row>
     <row r="11">
@@ -1631,13 +1631,13 @@
         <v>0.129</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1457.566457302651</v>
+        <v>1910.493578846438</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.410894379859082</v>
+        <v>3.41157988044196</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>57.36382025176147</v>
+        <v>57.3552514944755</v>
       </c>
     </row>
     <row r="12">
@@ -1668,13 +1668,13 @@
         <v>0.129</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1749.70121308147</v>
+        <v>2192.12766994567</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>5.836011711462684</v>
+        <v>5.833609376378724</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>27.04985360671645</v>
+        <v>27.07988279526595</v>
       </c>
     </row>
     <row r="13">
@@ -1705,13 +1705,13 @@
         <v>0.067</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1168.441733080299</v>
+        <v>1565.435703470746</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2.096233734403653</v>
+        <v>2.098482687301259</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>47.59415663990868</v>
+        <v>47.53793281746852</v>
       </c>
     </row>
     <row r="14">
@@ -1742,13 +1742,13 @@
         <v>0.067</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1165.379565795484</v>
+        <v>1554.64088887371</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1.823195697994828</v>
+        <v>1.822850724835316</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>54.4201075501293</v>
+        <v>54.42873187911709</v>
       </c>
     </row>
     <row r="15">
@@ -1779,13 +1779,13 @@
         <v>0.067</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>798.4204722315221</v>
+        <v>1190.643631827538</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1.073951765425783</v>
+        <v>1.074600492486508</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>73.15120586435543</v>
+        <v>73.13498768783731</v>
       </c>
     </row>
     <row r="16">
@@ -1816,13 +1816,13 @@
         <v>0.067</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1532.740350712013</v>
+        <v>1919.410342079188</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>2.752414298716123</v>
+        <v>2.751199651030124</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>31.18964253209692</v>
+        <v>31.2200087242469</v>
       </c>
     </row>
     <row r="17">
@@ -1853,13 +1853,13 @@
         <v>0.067</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1120.472325072978</v>
+        <v>1509.714282746324</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.824759272250448</v>
+        <v>1.824407796619986</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>54.3810181937388</v>
+        <v>54.38980508450035</v>
       </c>
     </row>
     <row r="18">
@@ -1890,13 +1890,13 @@
         <v>0.067</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1479.756416339018</v>
+        <v>1869.017090210883</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>2.140388481994235</v>
+        <v>2.140043228128822</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>46.49028795014411</v>
+        <v>46.49891929677944</v>
       </c>
     </row>
     <row r="19">
@@ -1927,13 +1927,13 @@
         <v>0.067</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1438.27663740552</v>
+        <v>1833.589673544701</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2.307452824226991</v>
+        <v>2.309137844884044</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>42.31367939432523</v>
+        <v>42.2715538778989</v>
       </c>
     </row>
   </sheetData>
